--- a/data/macro/USA/US Consumer Sentiment.xlsx
+++ b/data/macro/USA/US Consumer Sentiment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8DE3B97-3420-4439-9E15-0AFB67F9EDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D832E46F-0AB0-41AB-BE07-B475EF63CFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{586DF7D0-555B-4D57-B9C4-61D266B9D418}"/>
   </bookViews>
@@ -6367,7 +6367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90BA518E-4188-4051-9904-37DCC06068B4}">
-  <dimension ref="A1:H827"/>
+  <dimension ref="A1:H832"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="10" bestFit="1" customWidth="1"/>
@@ -24460,7 +24460,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D771" s="12" t="str">
-        <f t="shared" ref="D771:D827" si="12">IF(
+        <f t="shared" ref="D771:D832" si="12">IF(
  AND(
   B771 &gt;= IF(
          YEAR(B771)&gt;=2007,
@@ -25911,6 +25911,129 @@
       </c>
       <c r="G827" s="13">
         <v>53.3</v>
+      </c>
+    </row>
+    <row r="828" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A828" s="10">
+        <v>46143</v>
+      </c>
+      <c r="B828" s="10">
+        <v>46150</v>
+      </c>
+      <c r="C828" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D828" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E828" s="13">
+        <v>48.2</v>
+      </c>
+      <c r="F828" s="13">
+        <v>49.7</v>
+      </c>
+      <c r="G828" s="13">
+        <v>49.8</v>
+      </c>
+      <c r="H828" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="829" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A829" s="10">
+        <v>46143</v>
+      </c>
+      <c r="B829" s="10">
+        <v>46164</v>
+      </c>
+      <c r="C829" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D829" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E829" s="13">
+        <v>44.8</v>
+      </c>
+      <c r="F829" s="13">
+        <v>48.2</v>
+      </c>
+      <c r="G829" s="13">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="830" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A830" s="10">
+        <v>46174</v>
+      </c>
+      <c r="B830" s="10">
+        <v>46185</v>
+      </c>
+      <c r="C830" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D830" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E830" s="13">
+        <v>48.9</v>
+      </c>
+      <c r="F830" s="13">
+        <v>46.1</v>
+      </c>
+      <c r="G830" s="13">
+        <v>44.8</v>
+      </c>
+      <c r="H830" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="831" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A831" s="10">
+        <v>46174</v>
+      </c>
+      <c r="B831" s="10">
+        <v>46199</v>
+      </c>
+      <c r="C831" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D831" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E831" s="13">
+        <v>49.5</v>
+      </c>
+      <c r="F831" s="13">
+        <v>48.9</v>
+      </c>
+      <c r="G831" s="13">
+        <v>44.8</v>
+      </c>
+    </row>
+    <row r="832" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A832" s="10">
+        <v>46204</v>
+      </c>
+      <c r="B832" s="10">
+        <v>46220</v>
+      </c>
+      <c r="C832" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D832" s="12" t="str">
+        <f t="shared" si="12"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="G832" s="13">
+        <v>49.5</v>
+      </c>
+      <c r="H832" s="14">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
